--- a/data/Mapeo_Sucursales_Completo.xlsx
+++ b/data/Mapeo_Sucursales_Completo.xlsx
@@ -1555,7 +1555,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>No encontrado</t>
+          <t>119090-MILLAN S A (SUPER.ATOMO E.GONZALEZ)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
